--- a/KNK업무시스템구축/참고자료/형태별업무진행순서.xlsx
+++ b/KNK업무시스템구축/참고자료/형태별업무진행순서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\top00\JR\Claude 코드\KNK업무시스템구축\참고자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF085724-4874-4472-BE99-724984F8CC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665CAC47-99DE-43B9-BBA0-7E8C7D50E3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34452" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{064EE91B-9D61-4F10-B9D7-767966E129AA}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{064EE91B-9D61-4F10-B9D7-767966E129AA}"/>
   </bookViews>
   <sheets>
     <sheet name="본사PO" sheetId="1" r:id="rId1"/>

--- a/KNK업무시스템구축/참고자료/형태별업무진행순서.xlsx
+++ b/KNK업무시스템구축/참고자료/형태별업무진행순서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\top00\JR\Claude 코드\KNK업무시스템구축\참고자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665CAC47-99DE-43B9-BBA0-7E8C7D50E3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633E743E-2BCF-4C24-9145-2039B8B499E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{064EE91B-9D61-4F10-B9D7-767966E129AA}"/>
   </bookViews>
@@ -429,19 +429,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 고객사국내 -&gt; 본사 -&gt; 본사제작 -&gt; 본사확인 -&gt; 본사출하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 고객사국내 -&gt; 본사 -&gt; 법인제작 -&gt; 본사입고 -&gt; 본사확인 -&gt; 본사출하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 고객사해외 -&gt; 본사 -&gt; 법인제작 -&gt; 본사입고 -&gt; 본사확인 -&gt; 본사수출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 고객사해외 -&gt; 법인PO -&gt; 본사PO -&gt; 본사 상품,제품 수출 -&gt; 법인제작 -&gt; 법인출하</t>
+    <t>1. 고객사국내 -&gt; 본사PO -&gt; 본사개발 -&gt; 본사제작 -&gt; 본사출하 -&gt; 국내고객사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 고객사국내 -&gt; 본사PO -&gt; 본사개발(VN협업) -&gt;VN제작 -&gt; 본사입고 -&gt; 본사최종제작 -&gt; 본사출하 -&gt; 국내고객사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 고객사해외 -&gt; 본사PO -&gt; VN제작 -&gt; 본사입고 -&gt; 본사최종제작 -&gt; 본사수출 -&gt; 해외고객사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 고객사해외 -&gt; 법인PO -&gt; 본사PO -&gt; 본사개발 -&gt; 본사 상품,제품 수출 -&gt; VN제작 -&gt; 법인출하</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
